--- a/data/dishes 2.0.xlsx
+++ b/data/dishes 2.0.xlsx
@@ -899,7 +899,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>bowl, süß, kalt, vegetarisch, cheat</t>
+          <t>bowl, kalt, vegetarisch, cheat</t>
         </is>
       </c>
       <c r="I7" s="12" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>lunch,dinner</t>
+          <t>breakfast,lunch,dinner</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>lunch,dinner</t>
+          <t>breakfast,lunch,dinner</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="G156" s="14" t="inlineStr">
         <is>
-          <t>breakfast,snack</t>
+          <t>snack</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>leicht verdaulich, süß, warm</t>
+          <t>leicht verdaulich, warm</t>
         </is>
       </c>
       <c r="I158" s="13" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="G170" s="14" t="inlineStr">
         <is>
-          <t>breakfast,snack</t>
+          <t>snack</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>süß, warm, vegetarisch</t>
+          <t>warm, vegetarisch</t>
         </is>
       </c>
       <c r="I179" s="13" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="G186" s="16" t="inlineStr">
         <is>
-          <t>lunch,dinner</t>
+          <t>breakfast,lunch,dinner</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -9714,7 +9714,7 @@
       </c>
       <c r="G190" s="16" t="inlineStr">
         <is>
-          <t>breakfast,lunch,dinner</t>
+          <t>lunch,dinner</t>
         </is>
       </c>
       <c r="I190" s="13" t="inlineStr">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="G193" s="16" t="inlineStr">
         <is>
-          <t>breakfast,snack</t>
+          <t>snack</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="G216" s="16" t="inlineStr">
         <is>
-          <t>lunch,dinner</t>
+          <t>breakfast,lunch,dinner</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -12665,7 +12665,7 @@
       </c>
       <c r="G239" s="16" t="inlineStr">
         <is>
-          <t>breakfast,snack,lunch,dinner</t>
+          <t>snack,lunch,dinner</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -12728,7 +12728,7 @@
       </c>
       <c r="G240" s="16" t="inlineStr">
         <is>
-          <t>breakfast,snack,lunch,dinner</t>
+          <t>snack,lunch,dinner</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>süß, warm, meal prep, vegetarisch</t>
+          <t>warm, meal prep, vegetarisch</t>
         </is>
       </c>
       <c r="I241" s="13" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="G243" s="16" t="inlineStr">
         <is>
-          <t>breakfast,snack,lunch,dinner</t>
+          <t>snack,lunch,dinner</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>süß, kalt, meal prep, to go, vegetarisch</t>
+          <t>kalt, meal prep, to go, vegetarisch</t>
         </is>
       </c>
       <c r="I246" s="13" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="G250" s="16" t="inlineStr">
         <is>
-          <t>breakfast,snack,lunch,dinner</t>
+          <t>snack,lunch,dinner</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="G251" s="16" t="inlineStr">
         <is>
-          <t>breakfast,snack,lunch,dinner</t>
+          <t>snack,lunch,dinner</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="G254" s="16" t="inlineStr">
         <is>
-          <t>breakfast,snack,lunch,dinner</t>
+          <t>snack,lunch,dinner</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">

--- a/data/dishes 2.0.xlsx
+++ b/data/dishes 2.0.xlsx
@@ -2186,7 +2186,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>snack</t>
+          <t>breakfast,snack,dessert</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>snack</t>
+          <t>breakfast,snack,dessert</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="G150" s="14" t="inlineStr">
         <is>
-          <t>snack</t>
+          <t>breakfast,snack,dessert</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="G151" s="14" t="inlineStr">
         <is>
-          <t>snack,lunch,dinner</t>
+          <t>breakfast,snack,lunch,dinner,dessert</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="G156" s="14" t="inlineStr">
         <is>
-          <t>snack</t>
+          <t>breakfast,snack,dessert</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="G162" s="14" t="inlineStr">
         <is>
-          <t>snack</t>
+          <t>breakfast,snack,dessert</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="G170" s="14" t="inlineStr">
         <is>
-          <t>snack</t>
+          <t>breakfast,snack,dessert</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="G184" s="16" t="inlineStr">
         <is>
-          <t>snack</t>
+          <t>breakfast,snack,dessert</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="G193" s="16" t="inlineStr">
         <is>
-          <t>snack</t>
+          <t>breakfast,snack,dessert</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -10705,7 +10705,7 @@
       </c>
       <c r="G207" s="16" t="inlineStr">
         <is>
-          <t>snack</t>
+          <t>breakfast,snack,dessert</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -10822,7 +10822,7 @@
       </c>
       <c r="G209" s="16" t="inlineStr">
         <is>
-          <t>snack</t>
+          <t>breakfast,snack,dessert</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -12665,7 +12665,7 @@
       </c>
       <c r="G239" s="16" t="inlineStr">
         <is>
-          <t>snack,lunch,dinner</t>
+          <t>breakfast,snack,lunch,dinner,dessert</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -12728,7 +12728,7 @@
       </c>
       <c r="G240" s="16" t="inlineStr">
         <is>
-          <t>snack,lunch,dinner</t>
+          <t>breakfast,snack,lunch,dinner,dessert</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="G243" s="16" t="inlineStr">
         <is>
-          <t>snack,lunch,dinner</t>
+          <t>breakfast,snack,lunch,dinner,dessert</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="G247" s="16" t="inlineStr">
         <is>
-          <t>snack,lunch,dinner</t>
+          <t>breakfast,snack,lunch,dinner,dessert</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="G248" s="16" t="inlineStr">
         <is>
-          <t>snack,lunch,dinner</t>
+          <t>breakfast,snack,lunch,dinner,dessert</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="G250" s="16" t="inlineStr">
         <is>
-          <t>snack,lunch,dinner</t>
+          <t>breakfast,snack,lunch,dinner,dessert</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="G251" s="16" t="inlineStr">
         <is>
-          <t>snack,lunch,dinner</t>
+          <t>breakfast,snack,lunch,dinner,dessert</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="G254" s="16" t="inlineStr">
         <is>
-          <t>snack,lunch,dinner</t>
+          <t>breakfast,snack,lunch,dinner,dessert</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -13622,7 +13622,7 @@
       </c>
       <c r="G255" s="16" t="inlineStr">
         <is>
-          <t>snack,lunch,dinner</t>
+          <t>breakfast,snack,lunch,dinner,dessert</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="G256" s="16" t="inlineStr">
         <is>
-          <t>snack,lunch,dinner</t>
+          <t>breakfast,snack,lunch,dinner,dessert</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">

--- a/data/dishes 2.0.xlsx
+++ b/data/dishes 2.0.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J256"/>
+  <dimension ref="A1:J257"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2226,12 +2226,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>snack</t>
+          <t>snack,dessert</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>leicht verdaulich, süß, kalt, vegetarisch</t>
+          <t>leicht verdaulich, süß, kalt, vegetarisch, dessert</t>
         </is>
       </c>
       <c r="I35" s="2" t="n"/>
@@ -13711,7 +13711,44 @@
       </c>
       <c r="J256" s="7" t="n"/>
     </row>
-    <row r="257" ht="15" customHeight="1"/>
+    <row r="257" ht="15" customHeight="1">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>chips</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Chips</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="D257" t="b">
+        <v>0</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="F257" t="n">
+        <v>2</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>snack,dessert</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>vegetarisch, dessert, cheat</t>
+        </is>
+      </c>
+    </row>
     <row r="258" ht="15" customHeight="1"/>
     <row r="259" ht="15" customHeight="1"/>
     <row r="260" ht="15" customHeight="1"/>

--- a/data/dishes 2.0.xlsx
+++ b/data/dishes 2.0.xlsx
@@ -759,7 +759,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>kalt, meal prep, to go, vegetarisch</t>
+          <t>bowl, kalt, meal prep, to go, vegetarisch</t>
         </is>
       </c>
       <c r="I4" s="10" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>süß, kalt, meal prep, cheat</t>
+          <t>bowl, süß, kalt, meal prep, cheat</t>
         </is>
       </c>
       <c r="I11" s="13" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>leicht verdaulich, kalt, meal prep, vegetarisch</t>
+          <t>bowl, leicht verdaulich, kalt, meal prep, vegetarisch</t>
         </is>
       </c>
       <c r="I12" s="12" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>kalt, meal prep, to go</t>
+          <t>bowl, kalt, meal prep, to go</t>
         </is>
       </c>
       <c r="I13" s="12" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>kalt, meal prep, to go</t>
+          <t>bowl, kalt, meal prep, to go</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>kalt, meal prep, vegetarisch, cheat</t>
+          <t>bowl, kalt, meal prep, vegetarisch, cheat</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>kalt, meal prep</t>
+          <t>bowl, kalt, meal prep</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>kalt, meal prep, to go, vegetarisch</t>
+          <t>bowl, kalt, meal prep, to go, vegetarisch</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>kalt, meal prep, to go</t>
+          <t>bowl, kalt, meal prep, to go</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>kalt, meal prep, to go, vegetarisch</t>
+          <t>bowl, kalt, meal prep, to go, vegetarisch</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>süß, kalt, meal prep, to go, vegetarisch</t>
+          <t>bowl, süß, kalt, meal prep, to go, vegetarisch</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>kalt, meal prep, to go</t>
+          <t>bowl, kalt, meal prep, to go</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>kalt, vegetarisch, cheat</t>
+          <t>bowl, kalt, vegetarisch, cheat</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>kalt, meal prep, to go, vegetarisch</t>
+          <t>bowl, kalt, meal prep, to go, vegetarisch</t>
         </is>
       </c>
       <c r="I173" s="13" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>leicht verdaulich, kalt, meal prep, to go, vegetarisch</t>
+          <t>bowl, leicht verdaulich, kalt, meal prep, to go, vegetarisch</t>
         </is>
       </c>
       <c r="J175" s="7" t="n"/>
@@ -8913,7 +8913,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>leicht verdaulich, kalt, meal prep, to go, vegetarisch</t>
+          <t>bowl, leicht verdaulich, kalt, meal prep, to go, vegetarisch</t>
         </is>
       </c>
       <c r="J176" s="7" t="n"/>
@@ -11557,7 +11557,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>leicht verdaulich, kalt, meal prep, to go</t>
+          <t>bowl, leicht verdaulich, kalt, meal prep, to go</t>
         </is>
       </c>
       <c r="I221" s="13" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>kalt</t>
+          <t>bowl, kalt</t>
         </is>
       </c>
       <c r="I222" s="13" t="inlineStr">
@@ -11684,7 +11684,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>kalt, meal prep, to go</t>
+          <t>bowl, kalt, meal prep, to go</t>
         </is>
       </c>
       <c r="I223" s="13" t="inlineStr">
@@ -11754,7 +11754,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>süß, kalt, meal prep, vegetarisch</t>
+          <t>bowl, süß, kalt, meal prep, vegetarisch</t>
         </is>
       </c>
       <c r="I224" s="13" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>warm, meal prep, to go, vegetarisch</t>
+          <t>bowl, warm, meal prep, to go, vegetarisch</t>
         </is>
       </c>
       <c r="I225" s="13" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>leicht verdaulich, kalt, meal prep, to go</t>
+          <t>bowl, leicht verdaulich, kalt, meal prep, to go</t>
         </is>
       </c>
       <c r="I226" s="13" t="inlineStr">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>kalt, meal prep, to go, vegetarisch</t>
+          <t>bowl, kalt, meal prep, to go, vegetarisch</t>
         </is>
       </c>
       <c r="I227" s="13" t="inlineStr">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>kalt, meal prep, to go, vegetarisch</t>
+          <t>bowl, kalt, meal prep, to go, vegetarisch</t>
         </is>
       </c>
       <c r="I228" s="13" t="inlineStr">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>kalt, meal prep, to go, vegetarisch</t>
+          <t>bowl, kalt, meal prep, to go, vegetarisch</t>
         </is>
       </c>
       <c r="I229" s="13" t="inlineStr">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>leicht verdaulich, kalt, vegetarisch</t>
+          <t>bowl, leicht verdaulich, kalt, vegetarisch</t>
         </is>
       </c>
       <c r="I230" s="13" t="inlineStr">
@@ -12181,7 +12181,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>kalt, meal prep, to go</t>
+          <t>bowl, kalt, meal prep, to go</t>
         </is>
       </c>
       <c r="I231" s="13" t="inlineStr">
@@ -12240,7 +12240,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>kalt</t>
+          <t>bowl, kalt</t>
         </is>
       </c>
       <c r="I232" s="13" t="inlineStr">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>kalt, meal prep, to go, vegetarisch</t>
+          <t>bowl, kalt, meal prep, to go, vegetarisch</t>
         </is>
       </c>
       <c r="I246" s="13" t="inlineStr">
@@ -13450,7 +13450,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>kalt, meal prep, to go, vegetarisch</t>
+          <t>bowl, kalt, meal prep, to go, vegetarisch</t>
         </is>
       </c>
       <c r="I252" s="13" t="inlineStr">
